--- a/CCTV Data Remastered.xlsx
+++ b/CCTV Data Remastered.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kuliah\Skripsi\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kuliah\Skripsi\Project\SUMO-dinamic-tuning-AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5116FFD-3A7C-4484-AF86-1A866B418F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559AF5DD-A8C5-45E9-8D20-68D703D6F1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9AC95A1-0791-4863-B684-AC15BB9D8B18}"/>
   </bookViews>
@@ -708,10 +708,18 @@
       <c r="D4" s="2">
         <v>57</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="E4" s="2">
+        <v>64</v>
+      </c>
+      <c r="F4" s="2">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2">
+        <v>88</v>
+      </c>
+      <c r="H4" s="2">
+        <v>71</v>
+      </c>
       <c r="I4" s="2">
         <f t="shared" ref="I4:I30" si="1">C4*6</f>
         <v>780</v>
@@ -722,19 +730,19 @@
       </c>
       <c r="K4" s="2">
         <f t="shared" ref="K4:K30" si="3">E4*6</f>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="L4" s="2">
         <f t="shared" ref="L4:L30" si="4">F4*6</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M4" s="2">
         <f t="shared" ref="M4:M30" si="5">G4*6</f>
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="N4" s="2">
         <f t="shared" ref="N4:N30" si="6">H4*6</f>
-        <v>0</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">

--- a/CCTV Data Remastered.xlsx
+++ b/CCTV Data Remastered.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kuliah\Skripsi\Project\SUMO-dinamic-tuning-AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kuliah\Skripsi\Data\Raw Video\Two Side\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559AF5DD-A8C5-45E9-8D20-68D703D6F1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02CC18A-2C84-4E21-B685-9DB9E4D9D25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9AC95A1-0791-4863-B684-AC15BB9D8B18}"/>
   </bookViews>
@@ -668,9 +668,11 @@
         <v>6</v>
       </c>
       <c r="G3" s="2">
-        <v>88</v>
+        <f>E3+D3</f>
+        <v>98</v>
       </c>
       <c r="H3" s="2">
+        <f>C3+F3</f>
         <v>71</v>
       </c>
       <c r="I3" s="2">
@@ -691,7 +693,7 @@
       </c>
       <c r="M3" s="2">
         <f t="shared" si="0"/>
-        <v>528</v>
+        <v>588</v>
       </c>
       <c r="N3" s="2">
         <f t="shared" si="0"/>
@@ -709,16 +711,18 @@
         <v>57</v>
       </c>
       <c r="E4" s="2">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="F4" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G4" s="2">
-        <v>88</v>
+        <f>E4+D4</f>
+        <v>217</v>
       </c>
       <c r="H4" s="2">
-        <v>71</v>
+        <f>C4+F4</f>
+        <v>140</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" ref="I4:I30" si="1">C4*6</f>
@@ -730,54 +734,68 @@
       </c>
       <c r="K4" s="2">
         <f t="shared" ref="K4:K30" si="3">E4*6</f>
-        <v>384</v>
+        <v>960</v>
       </c>
       <c r="L4" s="2">
         <f t="shared" ref="L4:L30" si="4">F4*6</f>
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="M4" s="2">
         <f t="shared" ref="M4:M30" si="5">G4*6</f>
-        <v>528</v>
+        <v>1302</v>
       </c>
       <c r="N4" s="2">
         <f t="shared" ref="N4:N30" si="6">H4*6</f>
-        <v>426</v>
+        <v>840</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="C5" s="2">
+        <v>114</v>
+      </c>
+      <c r="D5" s="2">
+        <v>56</v>
+      </c>
+      <c r="E5" s="2">
+        <v>172</v>
+      </c>
+      <c r="F5" s="2">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2">
+        <f>E5+D5</f>
+        <v>228</v>
+      </c>
+      <c r="H5" s="2">
+        <f>C5+F5</f>
+        <v>120</v>
+      </c>
       <c r="I5" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>684</v>
       </c>
       <c r="J5" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="K5" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="L5" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M5" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="N5" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">

--- a/CCTV Data Remastered.xlsx
+++ b/CCTV Data Remastered.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kuliah\Skripsi\Data\Raw Video\Two Side\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02CC18A-2C84-4E21-B685-9DB9E4D9D25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A2F29D-DBDC-4A55-855F-BDD48C73FD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9AC95A1-0791-4863-B684-AC15BB9D8B18}"/>
   </bookViews>
@@ -802,210 +802,294 @@
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="C6" s="2">
+        <v>127</v>
+      </c>
+      <c r="D6" s="2">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2">
+        <v>80</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" ref="G6:G30" si="7">E6+D6</f>
+        <v>115</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" ref="H6:H30" si="8">C6+F6</f>
+        <v>135</v>
+      </c>
       <c r="I6" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>762</v>
       </c>
       <c r="J6" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="K6" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="L6" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M6" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="N6" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="C7" s="2">
+        <v>126</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46</v>
+      </c>
+      <c r="E7" s="2">
+        <v>181</v>
+      </c>
+      <c r="F7" s="2">
+        <v>19</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="7"/>
+        <v>227</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="8"/>
+        <v>145</v>
+      </c>
       <c r="I7" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="J7" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="K7" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="L7" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M7" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1362</v>
       </c>
       <c r="N7" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>870</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="C8" s="2">
+        <v>154</v>
+      </c>
+      <c r="D8" s="2">
+        <v>82</v>
+      </c>
+      <c r="E8" s="2">
+        <v>217</v>
+      </c>
+      <c r="F8" s="2">
+        <v>14</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="7"/>
+        <v>299</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="8"/>
+        <v>168</v>
+      </c>
       <c r="I8" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>924</v>
       </c>
       <c r="J8" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>492</v>
       </c>
       <c r="K8" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1302</v>
       </c>
       <c r="L8" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M8" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="N8" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="C9" s="2">
+        <v>122</v>
+      </c>
+      <c r="D9" s="2">
+        <v>77</v>
+      </c>
+      <c r="E9" s="2">
+        <v>171</v>
+      </c>
+      <c r="F9" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" ref="G9" si="9">E9+D9</f>
+        <v>248</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" ref="H9" si="10">C9+F9</f>
+        <v>137</v>
+      </c>
       <c r="I9" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="I9" si="11">C9*6</f>
+        <v>732</v>
       </c>
       <c r="J9" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" ref="J9" si="12">D9*6</f>
+        <v>462</v>
       </c>
       <c r="K9" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" ref="K9" si="13">E9*6</f>
+        <v>1026</v>
       </c>
       <c r="L9" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" ref="L9" si="14">F9*6</f>
+        <v>90</v>
       </c>
       <c r="M9" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" ref="M9" si="15">G9*6</f>
+        <v>1488</v>
       </c>
       <c r="N9" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ref="N9" si="16">H9*6</f>
+        <v>822</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="C10" s="2">
+        <v>114</v>
+      </c>
+      <c r="D10" s="2">
+        <v>31</v>
+      </c>
+      <c r="E10" s="2">
+        <v>111</v>
+      </c>
+      <c r="F10" s="2">
+        <v>6</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="7"/>
+        <v>142</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
       <c r="I10" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>684</v>
       </c>
       <c r="J10" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="K10" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="L10" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M10" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="N10" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="C11" s="2">
+        <v>105</v>
+      </c>
+      <c r="D11" s="2">
+        <v>47</v>
+      </c>
+      <c r="E11" s="2">
+        <v>188</v>
+      </c>
+      <c r="F11" s="2">
+        <v>22</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="7"/>
+        <v>235</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="8"/>
+        <v>127</v>
+      </c>
       <c r="I11" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="J11" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="K11" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="L11" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="M11" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="N11" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>762</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1016,8 +1100,14 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="G12" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I12" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1051,8 +1141,14 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="G13" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I13" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1086,8 +1182,14 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="G14" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I14" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1121,8 +1223,14 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="G15" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I15" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1156,8 +1264,14 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="G16" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I16" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1191,8 +1305,14 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="G17" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I17" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1226,8 +1346,14 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="G18" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I18" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1261,8 +1387,14 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+      <c r="G19" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I19" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1296,8 +1428,14 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="G20" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I20" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1331,8 +1469,14 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="G21" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I21" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1366,8 +1510,14 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="G22" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I22" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1401,8 +1551,14 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="G23" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I23" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1436,8 +1592,14 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="G24" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I24" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1467,35 +1629,49 @@
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
+      <c r="C25" s="2">
+        <v>127</v>
+      </c>
+      <c r="D25" s="2">
+        <v>64</v>
+      </c>
+      <c r="E25" s="2">
+        <v>177</v>
+      </c>
+      <c r="F25" s="2">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" ref="G25" si="17">E25+D25</f>
+        <v>241</v>
+      </c>
+      <c r="H25" s="2">
+        <f t="shared" ref="H25" si="18">C25+F25</f>
+        <v>135</v>
+      </c>
       <c r="I25" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="I25" si="19">C25*6</f>
+        <v>762</v>
       </c>
       <c r="J25" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" ref="J25" si="20">D25*6</f>
+        <v>384</v>
       </c>
       <c r="K25" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" ref="K25" si="21">E25*6</f>
+        <v>1062</v>
       </c>
       <c r="L25" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" ref="L25" si="22">F25*6</f>
+        <v>48</v>
       </c>
       <c r="M25" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" ref="M25" si="23">G25*6</f>
+        <v>1446</v>
       </c>
       <c r="N25" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ref="N25" si="24">H25*6</f>
+        <v>810</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
@@ -1506,8 +1682,14 @@
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="G26" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I26" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1541,8 +1723,14 @@
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+      <c r="G27" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I27" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1576,8 +1764,14 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
+      <c r="G28" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I28" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1611,8 +1805,14 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
+      <c r="G29" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I29" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1646,8 +1846,14 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
+      <c r="G30" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="I30" s="2">
         <f t="shared" si="1"/>
         <v>0</v>

--- a/CCTV Data Remastered.xlsx
+++ b/CCTV Data Remastered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kuliah\Skripsi\Data\Raw Video\Two Side\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A2F29D-DBDC-4A55-855F-BDD48C73FD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0714998-D70A-4EA9-AE28-5AC1D258CDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9AC95A1-0791-4863-B684-AC15BB9D8B18}"/>
   </bookViews>
@@ -168,7 +168,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -230,11 +230,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -242,6 +253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -583,36 +595,36 @@
       <c r="A1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="6"/>
+      <c r="E1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="6"/>
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5" t="s">
+      <c r="H1" s="6"/>
+      <c r="I1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5" t="s">
+      <c r="J1" s="6"/>
+      <c r="K1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5" t="s">
+      <c r="L1" s="6"/>
+      <c r="M1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="5"/>
+      <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="7"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1096,533 +1108,637 @@
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="C12" s="2">
+        <v>101</v>
+      </c>
+      <c r="D12" s="2">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2">
+        <v>143</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
       <c r="G12" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="H12" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="I12" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="J12" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="K12" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="L12" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M12" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="N12" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>654</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="C13" s="2">
+        <v>120</v>
+      </c>
+      <c r="D13" s="2">
+        <v>64</v>
+      </c>
+      <c r="E13" s="2">
+        <v>146</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
       <c r="G13" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H13" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I13" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="J13" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="K13" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="L13" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M13" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="N13" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>768</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="C14" s="2">
+        <v>99</v>
+      </c>
+      <c r="D14" s="2">
+        <v>30</v>
+      </c>
+      <c r="E14" s="2">
+        <v>94</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
       <c r="G14" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="H14" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="I14" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="J14" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K14" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="L14" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M14" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="N14" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="C15" s="2">
+        <v>84</v>
+      </c>
+      <c r="D15" s="2">
+        <v>28</v>
+      </c>
+      <c r="E15" s="2">
+        <v>90</v>
+      </c>
+      <c r="F15" s="2">
+        <v>15</v>
+      </c>
       <c r="G15" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H15" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="I15" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="J15" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="K15" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="L15" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M15" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="N15" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="C16" s="2">
+        <v>136</v>
+      </c>
+      <c r="D16" s="2">
+        <v>47</v>
+      </c>
+      <c r="E16" s="2">
+        <v>175</v>
+      </c>
+      <c r="F16" s="2">
+        <v>17</v>
+      </c>
       <c r="G16" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="H16" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="I16" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="J16" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="K16" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="L16" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M16" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1332</v>
       </c>
       <c r="N16" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>918</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="C17" s="2">
+        <v>145</v>
+      </c>
+      <c r="D17" s="2">
+        <v>54</v>
+      </c>
+      <c r="E17" s="2">
+        <v>113</v>
+      </c>
+      <c r="F17" s="2">
+        <v>9</v>
+      </c>
       <c r="G17" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="H17" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="I17" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="J17" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="K17" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="L17" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M17" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="N17" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>924</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="C18" s="2">
+        <v>101</v>
+      </c>
+      <c r="D18" s="2">
+        <v>34</v>
+      </c>
+      <c r="E18" s="2">
+        <v>106</v>
+      </c>
+      <c r="F18" s="2">
+        <v>4</v>
+      </c>
       <c r="G18" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="H18" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I18" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="J18" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="K18" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="L18" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M18" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="N18" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="C19" s="2">
+        <v>92</v>
+      </c>
+      <c r="D19" s="2">
+        <v>31</v>
+      </c>
+      <c r="E19" s="2">
+        <v>166</v>
+      </c>
+      <c r="F19" s="2">
+        <v>14</v>
+      </c>
       <c r="G19" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="H19" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="I19" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="J19" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="K19" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>996</v>
       </c>
       <c r="L19" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M19" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1182</v>
       </c>
       <c r="N19" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>636</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="C20" s="2">
+        <v>134</v>
+      </c>
+      <c r="D20" s="2">
+        <v>49</v>
+      </c>
+      <c r="E20" s="5">
+        <v>215</v>
+      </c>
+      <c r="F20" s="2">
+        <v>9</v>
+      </c>
       <c r="G20" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="H20" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="I20" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="J20" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="K20" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>E20*6</f>
+        <v>1290</v>
       </c>
       <c r="L20" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M20" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="N20" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>858</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="C21" s="2">
+        <v>152</v>
+      </c>
+      <c r="D21" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2">
+        <v>135</v>
+      </c>
+      <c r="F21" s="2">
+        <v>11</v>
+      </c>
       <c r="G21" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="H21" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>912</v>
       </c>
       <c r="J21" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="K21" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="L21" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M21" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1248</v>
       </c>
       <c r="N21" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>978</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="C22" s="2">
+        <v>98</v>
+      </c>
+      <c r="D22" s="2">
+        <v>48</v>
+      </c>
+      <c r="E22" s="2">
+        <v>111</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
       <c r="G22" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H22" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="I22" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="J22" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="K22" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="L22" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M22" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="N22" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>612</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="C23" s="2">
+        <v>71</v>
+      </c>
+      <c r="D23" s="2">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2">
+        <v>132</v>
+      </c>
+      <c r="F23" s="2">
+        <v>9</v>
+      </c>
       <c r="G23" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="H23" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I23" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="J23" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="K23" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="L23" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M23" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>978</v>
       </c>
       <c r="N23" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="C24" s="2">
+        <v>101</v>
+      </c>
+      <c r="D24" s="2">
+        <v>54</v>
+      </c>
+      <c r="E24" s="2">
+        <v>142</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8</v>
+      </c>
       <c r="G24" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H24" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="I24" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="J24" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="K24" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="L24" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M24" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1176</v>
       </c>
       <c r="N24" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>654</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
@@ -1642,35 +1758,35 @@
         <v>8</v>
       </c>
       <c r="G25" s="2">
-        <f t="shared" ref="G25" si="17">E25+D25</f>
+        <f t="shared" si="7"/>
         <v>241</v>
       </c>
       <c r="H25" s="2">
-        <f t="shared" ref="H25" si="18">C25+F25</f>
+        <f t="shared" ref="H25" si="17">C25+F25</f>
         <v>135</v>
       </c>
       <c r="I25" s="2">
-        <f t="shared" ref="I25" si="19">C25*6</f>
+        <f t="shared" ref="I25" si="18">C25*6</f>
         <v>762</v>
       </c>
       <c r="J25" s="2">
-        <f t="shared" ref="J25" si="20">D25*6</f>
+        <f t="shared" ref="J25" si="19">D25*6</f>
         <v>384</v>
       </c>
       <c r="K25" s="2">
-        <f t="shared" ref="K25" si="21">E25*6</f>
+        <f t="shared" ref="K25" si="20">E25*6</f>
         <v>1062</v>
       </c>
       <c r="L25" s="2">
-        <f t="shared" ref="L25" si="22">F25*6</f>
+        <f t="shared" ref="L25" si="21">F25*6</f>
         <v>48</v>
       </c>
       <c r="M25" s="2">
-        <f t="shared" ref="M25" si="23">G25*6</f>
+        <f t="shared" ref="M25" si="22">G25*6</f>
         <v>1446</v>
       </c>
       <c r="N25" s="2">
-        <f t="shared" ref="N25" si="24">H25*6</f>
+        <f t="shared" ref="N25" si="23">H25*6</f>
         <v>810</v>
       </c>
     </row>
@@ -1678,205 +1794,245 @@
       <c r="B26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="C26" s="2">
+        <v>153</v>
+      </c>
+      <c r="D26" s="2">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>145</v>
+      </c>
+      <c r="F26" s="2">
+        <v>10</v>
+      </c>
       <c r="G26" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="H26" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>918</v>
       </c>
       <c r="J26" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="K26" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="L26" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M26" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1284</v>
       </c>
       <c r="N26" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>978</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+      <c r="C27" s="2">
+        <v>64</v>
+      </c>
+      <c r="D27" s="2">
+        <v>38</v>
+      </c>
+      <c r="E27" s="2">
+        <v>121</v>
+      </c>
+      <c r="F27" s="2">
+        <v>5</v>
+      </c>
       <c r="G27" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="H27" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I27" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="J27" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="K27" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="L27" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M27" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="N27" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="C28" s="2">
+        <v>137</v>
+      </c>
+      <c r="D28" s="2">
+        <v>55</v>
+      </c>
+      <c r="E28" s="2">
+        <v>215</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
       <c r="G28" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="H28" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="I28" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>822</v>
       </c>
       <c r="J28" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="K28" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="L28" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M28" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="N28" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>882</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+      <c r="C29" s="2">
+        <v>140</v>
+      </c>
+      <c r="D29" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2">
+        <v>181</v>
+      </c>
+      <c r="F29" s="2">
+        <v>8</v>
+      </c>
       <c r="G29" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H29" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="I29" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="J29" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="K29" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="L29" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M29" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="N29" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>888</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
+      <c r="C30" s="2">
+        <v>121</v>
+      </c>
+      <c r="D30" s="2">
+        <v>29</v>
+      </c>
+      <c r="E30" s="2">
+        <v>87</v>
+      </c>
+      <c r="F30" s="2">
+        <v>3</v>
+      </c>
       <c r="G30" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="H30" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="I30" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="J30" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="K30" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>522</v>
       </c>
       <c r="L30" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M30" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>696</v>
       </c>
       <c r="N30" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>

--- a/CCTV Data Remastered.xlsx
+++ b/CCTV Data Remastered.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kuliah\Skripsi\Project\SUMO-dinamic-tuning-AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kuliah\Skripsi\Data\Raw Video\Two Side\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7110E722-2688-41A1-9E83-7D86232270DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0714998-D70A-4EA9-AE28-5AC1D258CDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F9AC95A1-0791-4863-B684-AC15BB9D8B18}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>Selatan</t>
   </si>
@@ -58,6 +58,78 @@
   </si>
   <si>
     <t>Senin Malam</t>
+  </si>
+  <si>
+    <t>Selasa Pagi</t>
+  </si>
+  <si>
+    <t>Selasa Siang</t>
+  </si>
+  <si>
+    <t>Selasa Sore</t>
+  </si>
+  <si>
+    <t>Selasa Malam</t>
+  </si>
+  <si>
+    <t>Rabu Pagi</t>
+  </si>
+  <si>
+    <t>Rabu Siang</t>
+  </si>
+  <si>
+    <t>Rabu Sore</t>
+  </si>
+  <si>
+    <t>Rabu Malam</t>
+  </si>
+  <si>
+    <t>Kamis Pagi</t>
+  </si>
+  <si>
+    <t>Kamis Siang</t>
+  </si>
+  <si>
+    <t>Kamis Sore</t>
+  </si>
+  <si>
+    <t>Kamis Malam</t>
+  </si>
+  <si>
+    <t>Jumat Pagi</t>
+  </si>
+  <si>
+    <t>Jumat Siang</t>
+  </si>
+  <si>
+    <t>Jumat Sore</t>
+  </si>
+  <si>
+    <t>Jumat Malam</t>
+  </si>
+  <si>
+    <t>Sabtu Pagi</t>
+  </si>
+  <si>
+    <t>Sabtu Siang</t>
+  </si>
+  <si>
+    <t>Sabtu Sore</t>
+  </si>
+  <si>
+    <t>Sabtu Malam</t>
+  </si>
+  <si>
+    <t>Minggu Pagi</t>
+  </si>
+  <si>
+    <t>Minggu Siang</t>
+  </si>
+  <si>
+    <t>Minggu Sore</t>
+  </si>
+  <si>
+    <t>Minggu Malam</t>
   </si>
   <si>
     <t>Dari Selatan</t>
@@ -527,11 +599,11 @@
         <v>4</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F1" s="6"/>
       <c r="G1" s="6" t="s">
@@ -539,15 +611,15 @@
       </c>
       <c r="H1" s="6"/>
       <c r="I1" s="6" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="J1" s="6"/>
       <c r="K1" s="6" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="6" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="N1" s="6"/>
     </row>
@@ -788,364 +860,1180 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>126</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46</v>
+      </c>
+      <c r="E7" s="2">
+        <v>181</v>
+      </c>
+      <c r="F7" s="2">
+        <v>19</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="7"/>
+        <v>227</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="8"/>
+        <v>145</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="1"/>
+        <v>756</v>
+      </c>
+      <c r="J7" s="2">
+        <f t="shared" si="2"/>
+        <v>276</v>
+      </c>
+      <c r="K7" s="2">
+        <f t="shared" si="3"/>
+        <v>1086</v>
+      </c>
+      <c r="L7" s="2">
+        <f t="shared" si="4"/>
+        <v>114</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="5"/>
+        <v>1362</v>
+      </c>
+      <c r="N7" s="2">
+        <f t="shared" si="6"/>
+        <v>870</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2">
+        <v>154</v>
+      </c>
+      <c r="D8" s="2">
+        <v>82</v>
+      </c>
+      <c r="E8" s="2">
+        <v>217</v>
+      </c>
+      <c r="F8" s="2">
+        <v>14</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="7"/>
+        <v>299</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="8"/>
+        <v>168</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="1"/>
+        <v>924</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" si="2"/>
+        <v>492</v>
+      </c>
+      <c r="K8" s="2">
+        <f t="shared" si="3"/>
+        <v>1302</v>
+      </c>
+      <c r="L8" s="2">
+        <f t="shared" si="4"/>
+        <v>84</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="5"/>
+        <v>1794</v>
+      </c>
+      <c r="N8" s="2">
+        <f t="shared" si="6"/>
+        <v>1008</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2">
+        <v>122</v>
+      </c>
+      <c r="D9" s="2">
+        <v>77</v>
+      </c>
+      <c r="E9" s="2">
+        <v>171</v>
+      </c>
+      <c r="F9" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" ref="G9" si="9">E9+D9</f>
+        <v>248</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" ref="H9" si="10">C9+F9</f>
+        <v>137</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" ref="I9" si="11">C9*6</f>
+        <v>732</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" ref="J9" si="12">D9*6</f>
+        <v>462</v>
+      </c>
+      <c r="K9" s="2">
+        <f t="shared" ref="K9" si="13">E9*6</f>
+        <v>1026</v>
+      </c>
+      <c r="L9" s="2">
+        <f t="shared" ref="L9" si="14">F9*6</f>
+        <v>90</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" ref="M9" si="15">G9*6</f>
+        <v>1488</v>
+      </c>
+      <c r="N9" s="2">
+        <f t="shared" ref="N9" si="16">H9*6</f>
+        <v>822</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2">
+        <v>114</v>
+      </c>
+      <c r="D10" s="2">
+        <v>31</v>
+      </c>
+      <c r="E10" s="2">
+        <v>111</v>
+      </c>
+      <c r="F10" s="2">
+        <v>6</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="7"/>
+        <v>142</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="1"/>
+        <v>684</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" si="2"/>
+        <v>186</v>
+      </c>
+      <c r="K10" s="2">
+        <f t="shared" si="3"/>
+        <v>666</v>
+      </c>
+      <c r="L10" s="2">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" si="5"/>
+        <v>852</v>
+      </c>
+      <c r="N10" s="2">
+        <f t="shared" si="6"/>
+        <v>720</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2">
+        <v>105</v>
+      </c>
+      <c r="D11" s="2">
+        <v>47</v>
+      </c>
+      <c r="E11" s="2">
+        <v>188</v>
+      </c>
+      <c r="F11" s="2">
+        <v>22</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="7"/>
+        <v>235</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="8"/>
+        <v>127</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="1"/>
+        <v>630</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" si="2"/>
+        <v>282</v>
+      </c>
+      <c r="K11" s="2">
+        <f t="shared" si="3"/>
+        <v>1128</v>
+      </c>
+      <c r="L11" s="2">
+        <f t="shared" si="4"/>
+        <v>132</v>
+      </c>
+      <c r="M11" s="2">
+        <f t="shared" si="5"/>
+        <v>1410</v>
+      </c>
+      <c r="N11" s="2">
+        <f t="shared" si="6"/>
+        <v>762</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2">
+        <v>101</v>
+      </c>
+      <c r="D12" s="2">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2">
+        <v>143</v>
+      </c>
+      <c r="F12" s="2">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="7"/>
+        <v>198</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="8"/>
+        <v>109</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="1"/>
+        <v>606</v>
+      </c>
+      <c r="J12" s="2">
+        <f t="shared" si="2"/>
+        <v>330</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" si="3"/>
+        <v>858</v>
+      </c>
+      <c r="L12" s="2">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="5"/>
+        <v>1188</v>
+      </c>
+      <c r="N12" s="2">
+        <f t="shared" si="6"/>
+        <v>654</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2">
+        <v>120</v>
+      </c>
+      <c r="D13" s="2">
+        <v>64</v>
+      </c>
+      <c r="E13" s="2">
+        <v>146</v>
+      </c>
+      <c r="F13" s="2">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="7"/>
+        <v>210</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="8"/>
+        <v>128</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="1"/>
+        <v>720</v>
+      </c>
+      <c r="J13" s="2">
+        <f t="shared" si="2"/>
+        <v>384</v>
+      </c>
+      <c r="K13" s="2">
+        <f t="shared" si="3"/>
+        <v>876</v>
+      </c>
+      <c r="L13" s="2">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="M13" s="2">
+        <f t="shared" si="5"/>
+        <v>1260</v>
+      </c>
+      <c r="N13" s="2">
+        <f t="shared" si="6"/>
+        <v>768</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="2">
+        <v>99</v>
+      </c>
+      <c r="D14" s="2">
+        <v>30</v>
+      </c>
+      <c r="E14" s="2">
+        <v>94</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="7"/>
+        <v>124</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="8"/>
+        <v>107</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="1"/>
+        <v>594</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="K14" s="2">
+        <f t="shared" si="3"/>
+        <v>564</v>
+      </c>
+      <c r="L14" s="2">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="M14" s="2">
+        <f t="shared" si="5"/>
+        <v>744</v>
+      </c>
+      <c r="N14" s="2">
+        <f t="shared" si="6"/>
+        <v>642</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="2">
+        <v>84</v>
+      </c>
+      <c r="D15" s="2">
+        <v>28</v>
+      </c>
+      <c r="E15" s="2">
+        <v>90</v>
+      </c>
+      <c r="F15" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="7"/>
+        <v>118</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="8"/>
+        <v>99</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="1"/>
+        <v>504</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" si="2"/>
+        <v>168</v>
+      </c>
+      <c r="K15" s="2">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="L15" s="2">
+        <f t="shared" si="4"/>
+        <v>90</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="5"/>
+        <v>708</v>
+      </c>
+      <c r="N15" s="2">
+        <f t="shared" si="6"/>
+        <v>594</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="2">
+        <v>136</v>
+      </c>
+      <c r="D16" s="2">
+        <v>47</v>
+      </c>
+      <c r="E16" s="2">
+        <v>175</v>
+      </c>
+      <c r="F16" s="2">
+        <v>17</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="7"/>
+        <v>222</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="8"/>
+        <v>153</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="1"/>
+        <v>816</v>
+      </c>
+      <c r="J16" s="2">
+        <f t="shared" si="2"/>
+        <v>282</v>
+      </c>
+      <c r="K16" s="2">
+        <f t="shared" si="3"/>
+        <v>1050</v>
+      </c>
+      <c r="L16" s="2">
+        <f t="shared" si="4"/>
+        <v>102</v>
+      </c>
+      <c r="M16" s="2">
+        <f t="shared" si="5"/>
+        <v>1332</v>
+      </c>
+      <c r="N16" s="2">
+        <f t="shared" si="6"/>
+        <v>918</v>
+      </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="2">
+        <v>145</v>
+      </c>
+      <c r="D17" s="2">
+        <v>54</v>
+      </c>
+      <c r="E17" s="2">
+        <v>113</v>
+      </c>
+      <c r="F17" s="2">
+        <v>9</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" si="7"/>
+        <v>167</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="8"/>
+        <v>154</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="1"/>
+        <v>870</v>
+      </c>
+      <c r="J17" s="2">
+        <f t="shared" si="2"/>
+        <v>324</v>
+      </c>
+      <c r="K17" s="2">
+        <f t="shared" si="3"/>
+        <v>678</v>
+      </c>
+      <c r="L17" s="2">
+        <f t="shared" si="4"/>
+        <v>54</v>
+      </c>
+      <c r="M17" s="2">
+        <f t="shared" si="5"/>
+        <v>1002</v>
+      </c>
+      <c r="N17" s="2">
+        <f t="shared" si="6"/>
+        <v>924</v>
+      </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="2">
+        <v>101</v>
+      </c>
+      <c r="D18" s="2">
+        <v>34</v>
+      </c>
+      <c r="E18" s="2">
+        <v>106</v>
+      </c>
+      <c r="F18" s="2">
+        <v>4</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="7"/>
+        <v>140</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="8"/>
+        <v>105</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="1"/>
+        <v>606</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" si="2"/>
+        <v>204</v>
+      </c>
+      <c r="K18" s="2">
+        <f t="shared" si="3"/>
+        <v>636</v>
+      </c>
+      <c r="L18" s="2">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="5"/>
+        <v>840</v>
+      </c>
+      <c r="N18" s="2">
+        <f t="shared" si="6"/>
+        <v>630</v>
+      </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="2">
+        <v>92</v>
+      </c>
+      <c r="D19" s="2">
+        <v>31</v>
+      </c>
+      <c r="E19" s="2">
+        <v>166</v>
+      </c>
+      <c r="F19" s="2">
+        <v>14</v>
+      </c>
+      <c r="G19" s="2">
+        <f t="shared" si="7"/>
+        <v>197</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="8"/>
+        <v>106</v>
+      </c>
+      <c r="I19" s="2">
+        <f t="shared" si="1"/>
+        <v>552</v>
+      </c>
+      <c r="J19" s="2">
+        <f t="shared" si="2"/>
+        <v>186</v>
+      </c>
+      <c r="K19" s="2">
+        <f t="shared" si="3"/>
+        <v>996</v>
+      </c>
+      <c r="L19" s="2">
+        <f t="shared" si="4"/>
+        <v>84</v>
+      </c>
+      <c r="M19" s="2">
+        <f t="shared" si="5"/>
+        <v>1182</v>
+      </c>
+      <c r="N19" s="2">
+        <f t="shared" si="6"/>
+        <v>636</v>
+      </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2">
+        <v>134</v>
+      </c>
+      <c r="D20" s="2">
+        <v>49</v>
+      </c>
+      <c r="E20" s="5">
+        <v>215</v>
+      </c>
+      <c r="F20" s="2">
+        <v>9</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" si="7"/>
+        <v>264</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="8"/>
+        <v>143</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="1"/>
+        <v>804</v>
+      </c>
+      <c r="J20" s="2">
+        <f t="shared" si="2"/>
+        <v>294</v>
+      </c>
+      <c r="K20" s="2">
+        <f>E20*6</f>
+        <v>1290</v>
+      </c>
+      <c r="L20" s="2">
+        <f t="shared" si="4"/>
+        <v>54</v>
+      </c>
+      <c r="M20" s="2">
+        <f t="shared" si="5"/>
+        <v>1584</v>
+      </c>
+      <c r="N20" s="2">
+        <f t="shared" si="6"/>
+        <v>858</v>
+      </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="2">
+        <v>152</v>
+      </c>
+      <c r="D21" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2">
+        <v>135</v>
+      </c>
+      <c r="F21" s="2">
+        <v>11</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" si="7"/>
+        <v>208</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="8"/>
+        <v>163</v>
+      </c>
+      <c r="I21" s="2">
+        <f t="shared" si="1"/>
+        <v>912</v>
+      </c>
+      <c r="J21" s="2">
+        <f t="shared" si="2"/>
+        <v>438</v>
+      </c>
+      <c r="K21" s="2">
+        <f t="shared" si="3"/>
+        <v>810</v>
+      </c>
+      <c r="L21" s="2">
+        <f t="shared" si="4"/>
+        <v>66</v>
+      </c>
+      <c r="M21" s="2">
+        <f t="shared" si="5"/>
+        <v>1248</v>
+      </c>
+      <c r="N21" s="2">
+        <f t="shared" si="6"/>
+        <v>978</v>
+      </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="2">
+        <v>98</v>
+      </c>
+      <c r="D22" s="2">
+        <v>48</v>
+      </c>
+      <c r="E22" s="2">
+        <v>111</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="7"/>
+        <v>159</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="8"/>
+        <v>102</v>
+      </c>
+      <c r="I22" s="2">
+        <f t="shared" si="1"/>
+        <v>588</v>
+      </c>
+      <c r="J22" s="2">
+        <f t="shared" si="2"/>
+        <v>288</v>
+      </c>
+      <c r="K22" s="2">
+        <f t="shared" si="3"/>
+        <v>666</v>
+      </c>
+      <c r="L22" s="2">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="M22" s="2">
+        <f t="shared" si="5"/>
+        <v>954</v>
+      </c>
+      <c r="N22" s="2">
+        <f t="shared" si="6"/>
+        <v>612</v>
+      </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="2">
+        <v>71</v>
+      </c>
+      <c r="D23" s="2">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2">
+        <v>132</v>
+      </c>
+      <c r="F23" s="2">
+        <v>9</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="7"/>
+        <v>163</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="8"/>
+        <v>80</v>
+      </c>
+      <c r="I23" s="2">
+        <f t="shared" si="1"/>
+        <v>426</v>
+      </c>
+      <c r="J23" s="2">
+        <f t="shared" si="2"/>
+        <v>186</v>
+      </c>
+      <c r="K23" s="2">
+        <f t="shared" si="3"/>
+        <v>792</v>
+      </c>
+      <c r="L23" s="2">
+        <f t="shared" si="4"/>
+        <v>54</v>
+      </c>
+      <c r="M23" s="2">
+        <f t="shared" si="5"/>
+        <v>978</v>
+      </c>
+      <c r="N23" s="2">
+        <f t="shared" si="6"/>
+        <v>480</v>
+      </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="2">
+        <v>101</v>
+      </c>
+      <c r="D24" s="2">
+        <v>54</v>
+      </c>
+      <c r="E24" s="2">
+        <v>142</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="7"/>
+        <v>196</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="8"/>
+        <v>109</v>
+      </c>
+      <c r="I24" s="2">
+        <f t="shared" si="1"/>
+        <v>606</v>
+      </c>
+      <c r="J24" s="2">
+        <f t="shared" si="2"/>
+        <v>324</v>
+      </c>
+      <c r="K24" s="2">
+        <f t="shared" si="3"/>
+        <v>852</v>
+      </c>
+      <c r="L24" s="2">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="M24" s="2">
+        <f t="shared" si="5"/>
+        <v>1176</v>
+      </c>
+      <c r="N24" s="2">
+        <f t="shared" si="6"/>
+        <v>654</v>
+      </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="2">
+        <v>127</v>
+      </c>
+      <c r="D25" s="2">
+        <v>64</v>
+      </c>
+      <c r="E25" s="2">
+        <v>177</v>
+      </c>
+      <c r="F25" s="2">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="7"/>
+        <v>241</v>
+      </c>
+      <c r="H25" s="2">
+        <f t="shared" ref="H25" si="17">C25+F25</f>
+        <v>135</v>
+      </c>
+      <c r="I25" s="2">
+        <f t="shared" ref="I25" si="18">C25*6</f>
+        <v>762</v>
+      </c>
+      <c r="J25" s="2">
+        <f t="shared" ref="J25" si="19">D25*6</f>
+        <v>384</v>
+      </c>
+      <c r="K25" s="2">
+        <f t="shared" ref="K25" si="20">E25*6</f>
+        <v>1062</v>
+      </c>
+      <c r="L25" s="2">
+        <f t="shared" ref="L25" si="21">F25*6</f>
+        <v>48</v>
+      </c>
+      <c r="M25" s="2">
+        <f t="shared" ref="M25" si="22">G25*6</f>
+        <v>1446</v>
+      </c>
+      <c r="N25" s="2">
+        <f t="shared" ref="N25" si="23">H25*6</f>
+        <v>810</v>
+      </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="2">
+        <v>153</v>
+      </c>
+      <c r="D26" s="2">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>145</v>
+      </c>
+      <c r="F26" s="2">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="7"/>
+        <v>214</v>
+      </c>
+      <c r="H26" s="2">
+        <f t="shared" si="8"/>
+        <v>163</v>
+      </c>
+      <c r="I26" s="2">
+        <f t="shared" si="1"/>
+        <v>918</v>
+      </c>
+      <c r="J26" s="2">
+        <f t="shared" si="2"/>
+        <v>414</v>
+      </c>
+      <c r="K26" s="2">
+        <f t="shared" si="3"/>
+        <v>870</v>
+      </c>
+      <c r="L26" s="2">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="M26" s="2">
+        <f t="shared" si="5"/>
+        <v>1284</v>
+      </c>
+      <c r="N26" s="2">
+        <f t="shared" si="6"/>
+        <v>978</v>
+      </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="2">
+        <v>64</v>
+      </c>
+      <c r="D27" s="2">
+        <v>38</v>
+      </c>
+      <c r="E27" s="2">
+        <v>121</v>
+      </c>
+      <c r="F27" s="2">
+        <v>5</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="7"/>
+        <v>159</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="8"/>
+        <v>69</v>
+      </c>
+      <c r="I27" s="2">
+        <f t="shared" si="1"/>
+        <v>384</v>
+      </c>
+      <c r="J27" s="2">
+        <f t="shared" si="2"/>
+        <v>228</v>
+      </c>
+      <c r="K27" s="2">
+        <f t="shared" si="3"/>
+        <v>726</v>
+      </c>
+      <c r="L27" s="2">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="M27" s="2">
+        <f t="shared" si="5"/>
+        <v>954</v>
+      </c>
+      <c r="N27" s="2">
+        <f t="shared" si="6"/>
+        <v>414</v>
+      </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="2">
+        <v>137</v>
+      </c>
+      <c r="D28" s="2">
+        <v>55</v>
+      </c>
+      <c r="E28" s="2">
+        <v>215</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2">
+        <f t="shared" si="7"/>
+        <v>270</v>
+      </c>
+      <c r="H28" s="2">
+        <f t="shared" si="8"/>
+        <v>147</v>
+      </c>
+      <c r="I28" s="2">
+        <f t="shared" si="1"/>
+        <v>822</v>
+      </c>
+      <c r="J28" s="2">
+        <f t="shared" si="2"/>
+        <v>330</v>
+      </c>
+      <c r="K28" s="2">
+        <f t="shared" si="3"/>
+        <v>1290</v>
+      </c>
+      <c r="L28" s="2">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="M28" s="2">
+        <f t="shared" si="5"/>
+        <v>1620</v>
+      </c>
+      <c r="N28" s="2">
+        <f t="shared" si="6"/>
+        <v>882</v>
+      </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="2">
+        <v>140</v>
+      </c>
+      <c r="D29" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2">
+        <v>181</v>
+      </c>
+      <c r="F29" s="2">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2">
+        <f t="shared" si="7"/>
+        <v>254</v>
+      </c>
+      <c r="H29" s="2">
+        <f t="shared" si="8"/>
+        <v>148</v>
+      </c>
+      <c r="I29" s="2">
+        <f t="shared" si="1"/>
+        <v>840</v>
+      </c>
+      <c r="J29" s="2">
+        <f t="shared" si="2"/>
+        <v>438</v>
+      </c>
+      <c r="K29" s="2">
+        <f t="shared" si="3"/>
+        <v>1086</v>
+      </c>
+      <c r="L29" s="2">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="M29" s="2">
+        <f t="shared" si="5"/>
+        <v>1524</v>
+      </c>
+      <c r="N29" s="2">
+        <f t="shared" si="6"/>
+        <v>888</v>
+      </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="2">
+        <v>121</v>
+      </c>
+      <c r="D30" s="2">
+        <v>29</v>
+      </c>
+      <c r="E30" s="2">
+        <v>87</v>
+      </c>
+      <c r="F30" s="2">
+        <v>3</v>
+      </c>
+      <c r="G30" s="2">
+        <f t="shared" si="7"/>
+        <v>116</v>
+      </c>
+      <c r="H30" s="2">
+        <f t="shared" si="8"/>
+        <v>124</v>
+      </c>
+      <c r="I30" s="2">
+        <f t="shared" si="1"/>
+        <v>726</v>
+      </c>
+      <c r="J30" s="2">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+      <c r="K30" s="2">
+        <f t="shared" si="3"/>
+        <v>522</v>
+      </c>
+      <c r="L30" s="2">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="M30" s="2">
+        <f t="shared" si="5"/>
+        <v>696</v>
+      </c>
+      <c r="N30" s="2">
+        <f t="shared" si="6"/>
+        <v>744</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
